--- a/derivatives/BAR/P8384_preprocessed.xlsx
+++ b/derivatives/BAR/P8384_preprocessed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>listno</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>trialno</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>conceptno</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>concept</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>concept_HU</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>responded</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>response_HU</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>similarity</t>
         </is>
@@ -569,7 +581,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.4549197554588318</v>
+        <v>0.4549197852611542</v>
       </c>
     </row>
     <row r="4">
@@ -861,7 +873,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.0611189641058445</v>
+        <v>0.0611189603805542</v>
       </c>
     </row>
     <row r="10">
@@ -1039,7 +1051,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.08847679942846298</v>
+        <v>0.08847679197788239</v>
       </c>
     </row>
     <row r="14">
@@ -1091,7 +1103,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.3618448674678802</v>
+        <v>0.3618448376655579</v>
       </c>
     </row>
     <row r="15">
@@ -1289,7 +1301,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.07937891781330109</v>
+        <v>0.07937892526388168</v>
       </c>
     </row>
     <row r="19">
@@ -1675,7 +1687,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.4684501886367798</v>
+        <v>0.4684502184391022</v>
       </c>
     </row>
     <row r="27">
@@ -1769,7 +1781,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.5086526274681091</v>
+        <v>0.5086525678634644</v>
       </c>
     </row>
     <row r="29">
@@ -2419,7 +2431,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.2719219624996185</v>
+        <v>0.2719219923019409</v>
       </c>
     </row>
     <row r="44">
@@ -2471,7 +2483,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.2124936133623123</v>
+        <v>0.2124936431646347</v>
       </c>
     </row>
     <row r="45">
@@ -2879,7 +2891,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.02899276278913021</v>
+        <v>0.02899277023971081</v>
       </c>
     </row>
     <row r="54">
@@ -2973,7 +2985,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.002470155945047736</v>
+        <v>0.002470165258273482</v>
       </c>
     </row>
     <row r="56">
@@ -3109,7 +3121,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-0.06221122667193413</v>
+        <v>-0.06221123412251472</v>
       </c>
     </row>
     <row r="59">
@@ -3161,7 +3173,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.05857935547828674</v>
+        <v>0.05857936292886734</v>
       </c>
     </row>
     <row r="60">
@@ -3391,7 +3403,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.06589366495609283</v>
+        <v>0.06589367985725403</v>
       </c>
     </row>
     <row r="65">
@@ -3527,7 +3539,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.6892604827880859</v>
+        <v>0.6892604231834412</v>
       </c>
     </row>
     <row r="68">
@@ -4783,7 +4795,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.1616200059652328</v>
+        <v>0.1616199910640717</v>
       </c>
     </row>
     <row r="96">
@@ -4835,7 +4847,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.2412681728601456</v>
+        <v>0.2412681579589844</v>
       </c>
     </row>
     <row r="97">
@@ -4929,7 +4941,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-0.04093906655907631</v>
+        <v>-0.04093906283378601</v>
       </c>
     </row>
     <row r="99">
@@ -5065,7 +5077,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.3312487304210663</v>
+        <v>0.3312487602233887</v>
       </c>
     </row>
   </sheetData>
